--- a/VerveStacks_CAN/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CAN/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2AFA829-6945-4163-8E30-1DEF5662FD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9928202-DCCD-47EB-AE96-3BD5338B6365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24146,7 +24146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{281182AB-3D28-4476-BA5D-B2F46E499FE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A63A18-2A7F-4335-9F37-EBA51816B508}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24203,7 +24203,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{957DFECE-0DF6-4CD0-A707-7CC01F783FAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BEE191F-15CB-490C-A204-1A161F3AA76C}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CAN/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87F2E50C-63F7-407D-A51B-FF0613A3A6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08E32A29-A18A-4E3F-8B5F-CAB2F3B9A26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -587,10 +587,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>FaP,SaP,WaD,FaD,RaD,RaP,SaD,WaP</t>
+    <t>RaP,FaP,SaP,FaD,WaD,WaP,SaD,RaD</t>
   </si>
   <si>
-    <t>RaP,FaN,WaP,SaN,WaN,FaP,SaP,RaN</t>
+    <t>RaP,SaN,WaN,WaP,FaN,RaN,FaP,SaP</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -24240,7 +24240,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E83570-93D0-4B6A-8ED9-C53611A01364}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F72764-9944-4CAC-B1AB-A8E0C99E0474}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24297,7 +24297,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{203B4206-C99A-4931-A373-42B4846377F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF19BB-8FBC-4FD6-A4A6-E9A76075DB7E}">
   <dimension ref="A9:AN126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24787,7 +24787,7 @@
         <v>161</v>
       </c>
       <c r="AM14">
-        <v>0.63794264990038052</v>
+        <v>0.63794264990038063</v>
       </c>
       <c r="AN14" t="s">
         <v>186</v>
@@ -25107,7 +25107,7 @@
         <v>161</v>
       </c>
       <c r="AM18">
-        <v>0.635020503846914</v>
+        <v>0.63502050384691389</v>
       </c>
       <c r="AN18" t="s">
         <v>186</v>
@@ -25427,7 +25427,7 @@
         <v>161</v>
       </c>
       <c r="AM22">
-        <v>0.63221619104040383</v>
+        <v>0.63221619104040372</v>
       </c>
       <c r="AN22" t="s">
         <v>186</v>
@@ -25565,7 +25565,7 @@
         <v>157</v>
       </c>
       <c r="AM28">
-        <v>0.52036666666666676</v>
+        <v>0.52036666666666664</v>
       </c>
       <c r="AN28" t="s">
         <v>186</v>
@@ -25657,7 +25657,7 @@
         <v>157</v>
       </c>
       <c r="AM32">
-        <v>0.53810000000000002</v>
+        <v>0.53809999999999991</v>
       </c>
       <c r="AN32" t="s">
         <v>186</v>
@@ -25703,7 +25703,7 @@
         <v>161</v>
       </c>
       <c r="AM34">
-        <v>0.62116666666666664</v>
+        <v>0.62116666666666676</v>
       </c>
       <c r="AN34" t="s">
         <v>186</v>
@@ -25927,7 +25927,7 @@
         <v>161</v>
       </c>
       <c r="AM50">
-        <v>0.63473333333333337</v>
+        <v>0.63473333333333326</v>
       </c>
       <c r="AN50" t="s">
         <v>186</v>
@@ -26039,7 +26039,7 @@
         <v>161</v>
       </c>
       <c r="AM58">
-        <v>0.76363333333333339</v>
+        <v>0.76363333333333328</v>
       </c>
       <c r="AN58" t="s">
         <v>186</v>
@@ -26067,7 +26067,7 @@
         <v>157</v>
       </c>
       <c r="AM60">
-        <v>0.61760000000000004</v>
+        <v>0.61759999999999993</v>
       </c>
       <c r="AN60" t="s">
         <v>186</v>
@@ -26347,7 +26347,7 @@
         <v>157</v>
       </c>
       <c r="AM80">
-        <v>0.62299999999999989</v>
+        <v>0.623</v>
       </c>
       <c r="AN80" t="s">
         <v>186</v>
@@ -26459,7 +26459,7 @@
         <v>157</v>
       </c>
       <c r="AM88">
-        <v>0.56653333333333333</v>
+        <v>0.56653333333333344</v>
       </c>
       <c r="AN88" t="s">
         <v>186</v>
@@ -26543,7 +26543,7 @@
         <v>161</v>
       </c>
       <c r="AM94">
-        <v>0.6490999999999999</v>
+        <v>0.64910000000000001</v>
       </c>
       <c r="AN94" t="s">
         <v>186</v>
@@ -26571,7 +26571,7 @@
         <v>157</v>
       </c>
       <c r="AM96">
-        <v>0.53186666666666671</v>
+        <v>0.5318666666666666</v>
       </c>
       <c r="AN96" t="s">
         <v>186</v>
@@ -26655,7 +26655,7 @@
         <v>161</v>
       </c>
       <c r="AM102">
-        <v>0.65540000000000009</v>
+        <v>0.65539999999999998</v>
       </c>
       <c r="AN102" t="s">
         <v>186</v>
@@ -26739,7 +26739,7 @@
         <v>157</v>
       </c>
       <c r="AM108">
-        <v>0.5442999999999999</v>
+        <v>0.54430000000000001</v>
       </c>
       <c r="AN108" t="s">
         <v>186</v>
